--- a/test.xlsx
+++ b/test.xlsx
@@ -400,10 +400,10 @@
         <v>8</v>
       </c>
       <c r="C2" s="3">
-        <v>46045.0</v>
+        <v>46048.0</v>
       </c>
       <c r="D2" s="3">
-        <v>46045.0</v>
+        <v>46048.0</v>
       </c>
       <c r="E2" s="4">
         <v>0.5416666666666666</v>

--- a/test.xlsx
+++ b/test.xlsx
@@ -479,12 +479,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -494,7 +494,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>jv15qh7fnuoqkba12ufevnk8cs</t>
+          <t>9nfipr7tosqr5lloapl54d97ds</t>
         </is>
       </c>
     </row>
@@ -515,12 +515,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>vcin6p6q528ae90nb45f84eid4</t>
+          <t>kl800sgvvohe7afaos08omcf18</t>
         </is>
       </c>
     </row>
@@ -551,12 +551,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>31nkpa45d0i08npbd5dudfcph4</t>
+          <t>62ka6kvsh4o8f2b2rj0c3ur3v0</t>
         </is>
       </c>
     </row>
@@ -600,11 +600,7 @@
           <t>synced</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>pdaftj3299qlknharlrg3g8ab4</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -616,10 +612,10 @@
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46052</v>
+        <v>46051</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46052</v>
+        <v>46051</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -636,11 +632,7 @@
           <t>synced</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>re57h36qaso40dgmj86r9nhtbc</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -652,19 +644,19 @@
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46027</v>
+        <v>46052</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46112</v>
+        <v>46111</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">

--- a/test.xlsx
+++ b/test.xlsx
@@ -479,24 +479,20 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>synced</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>9nfipr7tosqr5lloapl54d97ds</t>
-        </is>
-      </c>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -515,12 +511,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>17:00:00</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>18:00:00</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -566,7 +562,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>62ka6kvsh4o8f2b2rj0c3ur3v0</t>
+          <t>1tq4m9npttogk8p1u33u0dhu04</t>
         </is>
       </c>
     </row>
@@ -600,7 +596,11 @@
           <t>synced</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>pfeufgkqrl9sp8etvtdltftss4</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">

--- a/test.xlsx
+++ b/test.xlsx
@@ -511,12 +511,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -557,14 +557,10 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>synced</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>1tq4m9npttogk8p1u33u0dhu04</t>
-        </is>
-      </c>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -593,14 +589,10 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>synced</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>pfeufgkqrl9sp8etvtdltftss4</t>
-        </is>
-      </c>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -632,7 +624,11 @@
           <t>synced</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>tsgmv7ek1i7f7g4mae2cuju0ms</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -647,7 +643,7 @@
         <v>46052</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46111</v>
+        <v>46052</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -664,7 +660,11 @@
           <t>synced</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>umnctaabmhtbjq75ck7g54ij9g</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test.xlsx
+++ b/test.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>sync_flg</t>
+          <t>sync_status</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -479,20 +479,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>synced</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>r80dl1gdea0h9nj22nm1siie3o</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -511,7 +515,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -547,20 +551,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>18:00:00</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>19:00:00</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>synced</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>dqmum483esp3use2ausb1rv33s</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -579,20 +587,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>synced</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>qnm6loohkhr8ppcoadu52rll7o</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -611,12 +623,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -647,12 +659,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">

--- a/test.xlsx
+++ b/test.xlsx
@@ -489,7 +489,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>synced</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>synced</t>
+          <t>error</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">

--- a/test.xlsx
+++ b/test.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,6 +461,26 @@
           <t>eventId</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>repeat_pattern</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>interval</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>dayOfWeek</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>weekOfMonth</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -472,31 +492,41 @@
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46047</v>
+        <v>46056</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46047</v>
+        <v>46056</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>error</t>
+          <t>synced</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>r80dl1gdea0h9nj22nm1siie3o</t>
-        </is>
-      </c>
+          <t>jp7c13ljtriu4toi5muhengrtk</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -508,19 +538,19 @@
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46048</v>
+        <v>46057</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46048</v>
+        <v>46057</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -528,10 +558,22 @@
           <t>error</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>kl800sgvvohe7afaos08omcf18</t>
-        </is>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>MONTHLY_THE</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -544,10 +586,10 @@
         </is>
       </c>
       <c r="C4" s="1" t="n">
-        <v>46049</v>
+        <v>46056</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46049</v>
+        <v>46078</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -556,7 +598,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -566,9 +608,23 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>dqmum483esp3use2ausb1rv33s</t>
-        </is>
-      </c>
+          <t>k69rr2nhi1n6aa5lo2dbietse8</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>TU,TH</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -580,19 +636,19 @@
         </is>
       </c>
       <c r="C5" s="1" t="n">
-        <v>46050</v>
+        <v>46056</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46050</v>
+        <v>46056</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -602,9 +658,19 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>qnm6loohkhr8ppcoadu52rll7o</t>
-        </is>
-      </c>
+          <t>hbhmidnoft4ql4hhu96kd1b1nc</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -612,18 +678,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>説明会</t>
+          <t>内定者フォロー</t>
         </is>
       </c>
       <c r="C6" s="1" t="n">
-        <v>46051</v>
+        <v>46057</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46051</v>
+        <v>46142</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -638,9 +704,19 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>tsgmv7ek1i7f7g4mae2cuju0ms</t>
-        </is>
-      </c>
+          <t>p98p798qmo1pvnek1ke5918l2s</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MONTHLY_DAY</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -648,23 +724,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>アプコン会</t>
         </is>
       </c>
       <c r="C7" s="1" t="n">
-        <v>46052</v>
+        <v>46057</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46052</v>
+        <v>46057</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -674,9 +750,19 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>umnctaabmhtbjq75ck7g54ij9g</t>
-        </is>
-      </c>
+          <t>71tul0ef6o6l4f8kfb5cs9mhsc</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test.xlsx
+++ b/test.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,15 +468,10 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>interval</t>
+          <t>dayOfWeek</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
-        <is>
-          <t>dayOfWeek</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
         <is>
           <t>weekOfMonth</t>
         </is>
@@ -488,23 +483,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>進捗会</t>
+          <t>打ち合わせ</t>
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46056</v>
+        <v>46072</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>46056</v>
+        <v>46072</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -514,19 +509,16 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>jp7c13ljtriu4toi5muhengrtk</t>
+          <t>lruag24j924u6m86uhsf149sik</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>DAILY</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>1</v>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -534,235 +526,72 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1on1</t>
+          <t>アプコン会</t>
         </is>
       </c>
       <c r="C3" s="1" t="n">
-        <v>46057</v>
+        <v>46078</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46057</v>
+        <v>46079</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>synced</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>92uimqsmb3jbnhrmvasdlf3qj4</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MONTHLY_THE</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>TH</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>2</v>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>定例進捗会</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>46056</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>46078</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>09:00:00</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>synced</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>k69rr2nhi1n6aa5lo2dbietse8</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>WEEKLY</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>TU,TH</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>打ち合わせ</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>46056</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>46056</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>11:00:00</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>synced</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>hbhmidnoft4ql4hhu96kd1b1nc</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>内定者フォロー</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>46057</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>46142</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>17:00:00</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>18:00:00</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>synced</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>p98p798qmo1pvnek1ke5918l2s</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>MONTHLY_DAY</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>アプコン会</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>46057</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46057</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>18:30:00</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>21:00:00</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>synced</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>71tul0ef6o6l4f8kfb5cs9mhsc</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test.xlsx
+++ b/test.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,14 +494,14 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>09:00:00</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>10:00:00</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>11:00:00</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>synced</t>
@@ -509,7 +509,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>lruag24j924u6m86uhsf149sik</t>
+          <t>jmr66oubnd0n11cbl49s6j43d0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -533,16 +533,16 @@
         <v>46078</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>46079</v>
+        <v>46078</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>92uimqsmb3jbnhrmvasdlf3qj4</t>
+          <t>ds58oq11l0lr7cdjs363fe8hmk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -567,14 +567,42 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>進捗会</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>46072</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>46095</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>synced</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>f30qahpoe6a39jr1dp41q6et9k</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>DAILY</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
     </row>
@@ -582,16 +610,140 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>定例進捗会</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>46069</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>46095</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>synced</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>caallh5qvta0dtu0d1ksv50llo</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>WEEKLY</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>MO,TU</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>内定者フォロー</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>46072</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>46131</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>synced</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>dkati4u50p048ponsid3b4q1p8</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MONTHLY_DAY</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1on1</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>46072</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46165</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>synced</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>cjb44mnlm9cpa9p3n409a1ma1k</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MONTHLY_THE</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>WE</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
